--- a/it_forms/008_service_continuity_assessment--it_forms.xlsx
+++ b/it_forms/008_service_continuity_assessment--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'less_than_1_hour'}</t>
+          <t>less_than_1_hour</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Less than 1 hour'}</t>
+          <t>Less than 1 hour</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'1-4_hours'}</t>
+          <t>1-4_hours</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '1-4 hours'}</t>
+          <t>1-4 hours</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'more_than_4_hours'}</t>
+          <t>more_than_4_hours</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'More than 4 hours'}</t>
+          <t>More than 4 hours</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
